--- a/Data/list_spp.xlsx
+++ b/Data/list_spp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onetru-my.sharepoint.com/personal/jsingh_tru_ca/Documents/TRU_manuscript/Rachel/PRS_data/Rachel data/Rachel data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\TRU_Herbicide_impacts_on_community_characteristics\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{91574BA0-0E64-494D-A094-D123EE6B21BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76063F3C-6E7C-4BFA-8C11-56D3B094D097}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB7B8FF-FF91-4DD5-BF20-A497E86DDBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{20D6EF53-622C-3646-A384-F183B1AEEFA2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{20D6EF53-622C-3646-A384-F183B1AEEFA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -361,12 +361,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <i/>
       <sz val="12"/>
       <color theme="1"/>
@@ -382,9 +376,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <i/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -412,8 +410,8 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -426,8 +424,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -763,17 +761,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09AFB942-A100-EA44-9882-4CA67FA2CC97}">
   <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.8984375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" style="7"/>
-    <col min="5" max="5" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.8984375" style="7"/>
+    <col min="5" max="5" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -793,7 +791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -814,7 +812,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>90</v>
       </c>
@@ -835,7 +833,7 @@
         <v>TRUE</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -856,7 +854,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -877,7 +875,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -898,7 +896,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -919,7 +917,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -940,7 +938,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -961,7 +959,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -982,7 +980,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -1003,7 +1001,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1024,7 +1022,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -1045,7 +1043,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -1066,7 +1064,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -1087,7 +1085,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
@@ -1108,7 +1106,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
@@ -1129,7 +1127,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
@@ -1150,7 +1148,7 @@
         <v>TRUE</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
@@ -1171,7 +1169,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
@@ -1192,7 +1190,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
@@ -1213,7 +1211,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
@@ -1234,7 +1232,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
@@ -1255,7 +1253,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>11</v>
       </c>
@@ -1276,7 +1274,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>12</v>
       </c>
@@ -1297,7 +1295,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
@@ -1318,7 +1316,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1339,7 +1337,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>15</v>
       </c>
@@ -1360,7 +1358,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -1381,7 +1379,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>66</v>
       </c>
@@ -1402,11 +1400,11 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -1423,7 +1421,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -1444,7 +1442,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
@@ -1465,7 +1463,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>17</v>
       </c>
@@ -1486,7 +1484,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>18</v>
       </c>
@@ -1507,7 +1505,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>31</v>
       </c>
@@ -1528,7 +1526,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>32</v>
       </c>
@@ -1549,7 +1547,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>92</v>
       </c>
@@ -1570,7 +1568,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>94</v>
       </c>
@@ -1591,7 +1589,7 @@
         <v>FALSE</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>96</v>
       </c>
@@ -1629,6 +1627,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F3B68D6F0C44AC44AA7D7D98EA303BE5" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5ee2c84c17da6c439e63065f20e698a0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e0dd9ad3-02ee-4988-96cc-32ec19bb58de" xmlns:ns3="705b3587-fa16-4aed-b2e3-30bf12d47144" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1384afef40b06baa3baac2cca9ba515f" ns2:_="" ns3:_="">
     <xsd:import namespace="e0dd9ad3-02ee-4988-96cc-32ec19bb58de"/>
@@ -1817,15 +1824,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1838,13 +1836,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F77153C1-C596-4BA2-AF3A-863415FC13D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32B8EBF0-814D-46F8-986F-1A468A6A209C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32B8EBF0-814D-46F8-986F-1A468A6A209C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F77153C1-C596-4BA2-AF3A-863415FC13D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e0dd9ad3-02ee-4988-96cc-32ec19bb58de"/>
+    <ds:schemaRef ds:uri="705b3587-fa16-4aed-b2e3-30bf12d47144"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24B40716-0286-45D7-9C62-7F23DAB68A85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24B40716-0286-45D7-9C62-7F23DAB68A85}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e0dd9ad3-02ee-4988-96cc-32ec19bb58de"/>
+    <ds:schemaRef ds:uri="705b3587-fa16-4aed-b2e3-30bf12d47144"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>